--- a/www/download/COUNTRY.ESP.WIOD16.xlsx
+++ b/www/download/COUNTRY.ESP.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Espanha</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1.0827197921178</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>1.11656989727557</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1.0575296108291</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.884016973125884</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.803923144947343</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.803793907242183</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>0.796431984708506</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>0.729660707770887</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.67990209409845</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.716948666475481</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>0.75431847325941</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0.718390804597701</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0.778331257783312</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.75295534974776</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.752718407844284</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>16.691</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17.248</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>17.693</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>18.282</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>18.97</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>19.784</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>20.609</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>21.285</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>21.324</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>19.987</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>19.113</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>18.338</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>17.798</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>17.965</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>13.856</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>14.392</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>14.84</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>15.452</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>16.09</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>16.876</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>17.702</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>18.376</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>18.451</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>17.317</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>17.048</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>16.598</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>15.817</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>15.299</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>15.495</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>28651.032</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>29812.188</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>30680.005</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>31482.397</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>32390.788</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>33471.927</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>34629.169</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>35477.601</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>35675.77</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>33590.325</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>32842.848</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>32027.736</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>30425.323</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>29371.932</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>29690.137</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23621.694</t>
+          <t>38314544036.2029</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24701.869</t>
+          <t>38924706195.1575</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>25565.822</t>
+          <t>41492763073.8081</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>26488.219</t>
+          <t>42828041574.2672</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>27358.158</t>
+          <t>44889468423.7603</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>28448.156</t>
+          <t>46820867821.9649</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>29650.56</t>
+          <t>49581953211.1585</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>30541.522</t>
+          <t>50564829728.6382</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>30781.581</t>
+          <t>50300514818.8268</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>29022.181</t>
+          <t>41833236767.279</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>28418.43</t>
+          <t>44693977339.3388</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>27720.345</t>
+          <t>47448959368.7665</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>26150.167</t>
+          <t>44984470111.0056</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>25162.207</t>
+          <t>43393836439.0171</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>25534.535</t>
+          <t>43961487696.0317</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>12515348334.8921</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13382022053.7889</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>14456008610.3378</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>16184329980.1854</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>17822666074.3685</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>18400993287.3298</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>18660523100.9168</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>19149267049.9029</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>19778290061.8718</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>17651665055.452</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>16129372067.9217</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>16050971286.4322</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>14096203511.4385</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>14337194403.4132</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>14761777174.8412</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1785025.0642003</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1707828.19818785</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1560070.23315864</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1275369.29143952</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1125084.06731149</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1052216.87630838</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1006255.39139532</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>854484.911642472</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>797133.766078307</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>851111.596981077</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>953088.780305404</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>933997.717289911</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>976046.647885357</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>936460.747349605</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>954299.072231082</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>117289.995997886</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>119402.278139821</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>122576.379495656</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>136984.589877568</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>153833.792779233</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>169225.869944801</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>182072.03499863</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>207726.623022127</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>218384.797042163</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>179260.62204961</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>191999.225598032</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>194690.684989907</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>176214.854104046</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>168464.527903777</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>170598.486703693</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>311319.699758727</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>313304.715096243</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>335979.508183834</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>377412.252120832</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>437343.036265442</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>489768.800264381</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>547921.038331832</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>630902.192909868</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>681201.786210204</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>515564.312772881</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>610244.491657643</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>688006.260511743</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>635540.631770362</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>612458.800970001</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>623344.85161777</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.88741802208925</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.845899588321631</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.768525648339563</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.636658362281899</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.535020511849507</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.546011976407176</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.588945810342436</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.59491858985563</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.556331760921034</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.644161098050976</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.761905539802071</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.727019767547139</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.855121308285613</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.755030014380624</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.729773745909064</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>99175.1890001269</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>102905.999522474</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>114192.805157306</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>147503.869650379</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>179606.033801739</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>194950.993209483</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>217260.28230171</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>263183.625909465</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>309688.9159431</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>297988.796497027</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>312398.559633592</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>343068.703302047</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>323402.945907929</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>331446.970133385</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>336189.527003953</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0827197921178</t>
+          <t>903.250480653879</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656989727557</t>
+          <t>929.804274076342</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0575296108291</t>
+          <t>974.11800529227</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884016973125884</t>
+          <t>1047.38708526254</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923144947343</t>
+          <t>1107.65147598698</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793907242183</t>
+          <t>1090.39046240311</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431984708506</t>
+          <t>1054.17154951625</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660707770887</t>
+          <t>1042.09161233268</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.67990209409845</t>
+          <t>1071.9301321803</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948666475481</t>
+          <t>1019.29637969984</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.75431847325941</t>
+          <t>946.093009779315</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718390804597701</t>
+          <t>967.019187779077</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778331257783312</t>
+          <t>891.205886795124</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.75295534974776</t>
+          <t>937.132780143353</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.752718407844284</t>
+          <t>952.66159253717</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>8845878320.2266</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>10222003244.2407</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>12013618430.6515</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>13257262747.8307</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>13882375206.804</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>13629136166.9056</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>13607226203.0452</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>14969239675.836</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>16565164161.3284</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>16102905658.9849</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>15331365572.3435</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>16903386254.1073</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>16569080146.4107</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>17933279168.5296</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>18067772304.4811</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>9086681710.53335</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>10373004300.4325</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>12388482910.6689</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>13644250882.6224</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>14589533017.868</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>14335902488.5979</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>14276271311.8512</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>15473821781.8697</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>17105566509.1395</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.863</t>
+          <t>15734757224.4044</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>14421907990.9406</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>15660944926.3657</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>15265816373.5662</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>16314946649.5116</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>16597034810.0921</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>-240803390.306756</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.679</t>
+          <t>-151001056.191744</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-374864480.017388</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.539</t>
+          <t>-386988134.791714</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3.095</t>
+          <t>-707157811.064</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3.434</t>
+          <t>-706766321.692291</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3.841</t>
+          <t>-669045108.805968</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>4.529</t>
+          <t>-504582106.033709</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>5.144</t>
+          <t>-540402347.811139</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4.829</t>
+          <t>368148434.58044</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>4.621</t>
+          <t>909457581.402847</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>4.822</t>
+          <t>1242441327.74153</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>4.329</t>
+          <t>1303263772.84447</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>1618332519.01799</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>4.296</t>
+          <t>1470737494.38895</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1704.81123564691</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1716.32532673721</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1722.75267686875</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1714.21483164101</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>1700.2677356204</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2.309</t>
+          <t>1685.75671383536</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.578</t>
+          <t>1675.02146698604</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>1662.05128484202</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.313</t>
+          <t>1668.27891020048</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.865</t>
+          <t>1675.88745488668</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.702</t>
+          <t>1666.92651509819</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1670.06125289185</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2.524</t>
+          <t>1653.29503066321</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>1644.69615661154</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2.568</t>
+          <t>1647.88901150671</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.542</t>
+          <t>1716.5557628406</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1728.46319936894</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>1734.02919690784</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>1722.06221709557</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.966</t>
+          <t>1707.46534338101</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.038</t>
+          <t>1691.86854598169</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1680.27722032725</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1666.79667315964</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1673.02582938415</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.403</t>
+          <t>1680.62543869114</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.312</t>
+          <t>1672.2853352665</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1675.74813328981</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1659.16787615695</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1650.26612220264</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1652.71155721157</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>146898.354986238</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150032.25356041</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>162219.527082671</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>199523.146189194</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>233708.226768638</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>247410.933156313</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>274359.19385026</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>335425.079009996</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>366989.157141428</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>298261.990681314</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>323793.487801255</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>379223.565984864</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>357950.600244197</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>376907.394032158</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>389005.301877207</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6169576652.48873</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5948921163.28834</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6025399453.18681</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>5973243728.43654</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6219546213.38134</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6110165133.23113</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>6422833642.16909</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>6864992666.43665</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>7267063706.89547</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>6345505284.16596</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>8287037580.23246</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>9956737880.36356</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>10034100276.0753</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>10175253214.8249</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>10575935405.1325</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>175703.184176932</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>175184.645432379</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>186359.233496154</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>232337.172774374</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>286724.806841647</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>315348.00836092</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>358047.95499427</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>428777.454858508</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>455506.658798888</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>325355.569109811</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>349594.814690316</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>398275.125537332</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>357604.200563964</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>361523.211548035</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>382185.98288372</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>28651.032</t>
+          <t>19465828400.8983</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29812.188</t>
+          <t>20197568032.6603</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30680.005</t>
+          <t>21936990610.2099</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>31482.397</t>
+          <t>24223048535.7316</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>32390.788</t>
+          <t>27417943660.9585</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>33471.927</t>
+          <t>28305627664.4173</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>34629.169</t>
+          <t>29634764035.6863</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>35477.601</t>
+          <t>30964160151.2429</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>35675.77</t>
+          <t>31452830951.4281</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>33590.325</t>
+          <t>25085966480.6433</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>32842.848</t>
+          <t>25849773607.289</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>32027.736</t>
+          <t>28423291707.8444</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>30425.323</t>
+          <t>26574453825.6924</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>29371.932</t>
+          <t>26825643814.346</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>29690.137</t>
+          <t>28080595168.131</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23621.694</t>
+          <t>-28804.8291906938</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24701.869</t>
+          <t>-25152.3918719693</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>25565.822</t>
+          <t>-24139.7064134827</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>26488.219</t>
+          <t>-32814.0265851801</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>27358.158</t>
+          <t>-53016.5800730098</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>28448.156</t>
+          <t>-67937.0752046073</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>29650.56</t>
+          <t>-83688.7611440094</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>30541.522</t>
+          <t>-93352.3758485118</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>30781.581</t>
+          <t>-88517.5016574598</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>29022.181</t>
+          <t>-27093.5784284968</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>28418.43</t>
+          <t>-25801.3268890609</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>27720.345</t>
+          <t>-19051.5595524687</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>26150.167</t>
+          <t>346.399680232909</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>25162.207</t>
+          <t>15384.1824841238</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>25534.535</t>
+          <t>6819.31899348682</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>38322.13</t>
+          <t>-13296251748.4095</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>38932.853</t>
+          <t>-14248646869.372</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>41500.234</t>
+          <t>-15911591157.0231</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>42834.185</t>
+          <t>-18249804807.295</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>44894.016</t>
+          <t>-21198397447.5772</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>46821.43</t>
+          <t>-22195462531.1861</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>49580.943</t>
+          <t>-23211930393.5172</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>50562.082</t>
+          <t>-24099167484.8063</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>50302.038</t>
+          <t>-24185767244.5326</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>41836.951</t>
+          <t>-18740461196.4774</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>44698.752</t>
+          <t>-17562736027.0565</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>47445.792</t>
+          <t>-18466553827.4808</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>44980.368</t>
+          <t>-16540353549.6171</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>43392.507</t>
+          <t>-16650390599.5211</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>43961.238</t>
+          <t>-17504659762.9986</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>260765.5296</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>272757.6668</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>305968.7376</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>389745.9104</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>452040.7234</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>483844.1751</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>520190.0576</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>603141.9745</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>677882.8952</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>615625.6656</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>567582.5466</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>577132.944</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>501788.9184</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>507332.8719</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.623</t>
+          <t>504118.835758872</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14435.041</t>
+          <t>0.0664749332589795</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>14834.436</t>
+          <t>0.0692189275717676</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>15137.925</t>
+          <t>0.0704535837387792</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>15544.757</t>
+          <t>0.0683223738691372</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>15789.704</t>
+          <t>0.0644619479762061</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>16177.637</t>
+          <t>0.0617684983515631</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>16475.891</t>
+          <t>0.0590740508633274</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>16648.637</t>
+          <t>0.0576567643281089</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>16125.718</t>
+          <t>0.0524462751774361</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>14545.328</t>
+          <t>0.0501830742135464</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>14061.92</t>
+          <t>0.0414340054478446</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>13427.015</t>
+          <t>0.0401470185598312</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>12472.738</t>
+          <t>0.0416845393414433</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>11936.023</t>
+          <t>0.0428211099650654</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>12031.483</t>
+          <t>0.0428889973322069</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>289329.7068</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>302565.026</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>341068.464</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>436895.4576</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>511640.948</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>552435.1404</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>604134.4512</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>716162.998</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>823320.0116</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>765986.5004</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>717833.4075</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>739132.512</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>640603.8496</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>646293.303</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>652043.068069816</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12516.473</t>
+          <t>336799.88364</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>13383.342</t>
+          <t>351185.09012</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14457.356</t>
+          <t>394371.27408</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>16185.577</t>
+          <t>502174.86032</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>17823.225</t>
+          <t>586390.00875</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>18401.433</t>
+          <t>630805.35375</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>18660.954</t>
+          <t>685992.28872</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>19150.421</t>
+          <t>809004.09425</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>19779.129</t>
+          <t>929065.23672</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>17652.586</t>
+          <t>863020.08628</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>16130.699</t>
+          <t>808465.81599</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>16051.174</t>
+          <t>832683.4032</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>14095.829</t>
+          <t>725883.7344</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>14336.471</t>
+          <t>734126.93088</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>14760.859</t>
+          <t>739383.916686971</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>88.72</t>
+          <t>1587831.6499944</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>84.57</t>
+          <t>1679430.7464096</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.84</t>
+          <t>1940205.7568784</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>63.65</t>
+          <t>2539117.6009472</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>3095010.8771442</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>3434280.4407054</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>58.89</t>
+          <t>3840991.7867872</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>59.48</t>
+          <t>4528697.723213</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>55.63</t>
+          <t>5144392.5049796</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>64.41</t>
+          <t>4828920.6394924</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>76.18</t>
+          <t>4620921.5451645</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>4821965.178048</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>4328866.1586016</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>4309961.4287715</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>4296159.82321717</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>453400.117824481</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.708</t>
+          <t>467702.39938474</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>476990.84602619</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>490208.811002345</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>502635.71362318</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.052</t>
+          <t>522254.717589006</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>543388.598481588</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>567368.397796838</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>583268.334052341</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>560239.519807233</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>563248.87052</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>553843.305188354</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.976</t>
+          <t>525857.336096829</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>518526.114696681</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>521271.573089333</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>389240.563057236</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>403023.527368025</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>412603.868992711</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>426892.942980095</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>438950.311392502</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>457743.67341167</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>478576.314597624</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>502002.181893431</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>516380.942391679</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>496357.218287115</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>500106.31</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>491996.940119529</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>464987.739142334</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>457133.362979475</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>459914.61476196</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>204726.19196</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>219154.39472</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>250887.25392</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>320982.41168</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>379116.46395</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>407081.33895</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>444163.22648</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>524293.68325</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>579493.14088</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>540318.87932</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>503861.84811</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>536656.2288</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>503849.7376</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>516004.30242</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>520447.514200648</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>23621694000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>24701869000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>25565822000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>26488219000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>27358158000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>28448156000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>29650560000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>30541522000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>30781581000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>29022181000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>28418430000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>27720344700</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>26150167500</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>25162206500</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>25534534600</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>28651032237.5724</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>29812187570.0757</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>30680005177.9707</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>31482397040.4979</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>32390788310.4722</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>33471927313.7018</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>34629169289.1684</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>35477600508.5355</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>35675770088.3706</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>33590324518.032</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>32842847841.9665</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>32027736197.5015</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>30425322762.6033</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>29371931522.7992</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>29690136769.5273</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>14435041277.9848</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>14834435524.5254</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>15137925227.498</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>15544756900.028</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>15789704215.7987</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>16177637457.6443</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>16475890664.5509</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>16648636573.5607</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>16125717727.3991</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>14545328021.0932</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>14061919698.3481</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>13427015031.3635</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>12472738077.3081</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>11936022730.1082</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>12031483463.3219</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>16691000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>17247800</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>17692900</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>18281800</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>18970100</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>19784000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>20609200</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>21284900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>21324100</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>19986800</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>19639500</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>19112500</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>18337700</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>17798300</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>17964500</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>13855900</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>14392300</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14840100</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>15452100</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>16090500</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>16875600</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>17701600</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>18375800</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>18451100</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>17317500</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>17048400</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>16598400</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>15817000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>15299000</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>15495300</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>28651032237.5724</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>29812187570.0757</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>30680005177.9707</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>31482397040.4979</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>32390788310.4722</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>33471927313.7018</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>34629169289.1684</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>35477600508.5355</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>35675770088.3706</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>33590324518.032</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>32842847841.9665</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>32027736197.5015</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>30425322762.6033</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>29371931522.7992</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>29690136769.5273</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>23621694000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>24701869000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>25565822000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>26488219000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>27358158000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>28448156000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>29650560000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>30541522000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>30781581000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>29022181000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>28418430000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>27720344700</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>26150167500</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>25162206500</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>25534534600</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1114171.9296</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1180336.3168</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1359448.4592</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1750924.5264</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2091361.6066</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2308764.7011</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2578264.1072</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>3036474.318</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>3313043.186</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2864772.746</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2702194.1955</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2830211.616</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2524467.5456</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2549224.2012</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2567905.476</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>541526.0756</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>570339.5744</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>645258.528</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>823157.272</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>965506.4727</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1037886.6927</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1130155.5152</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1333297.7775</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1508558.3776</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1403338.9656</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1312327.6641</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1369339.632</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1229733.472</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1250131.2333</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1259828.5065</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2332598.82008332</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2444907.52164619</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2567037.39493812</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2686931.54649816</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2821778.30042932</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2953131.0902708</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3104352.96349403</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3211471.24884444</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3273458.25138887</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>3283994.51893211</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>3219343.093546</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>3177072.64836826</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>3102925.79397925</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2992531.1673824</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>3017575.49592806</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
